--- a/SBM-corps-FHIR/ig/StructureDefinition-PersonneStructure.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-PersonneStructure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-corps-FHIR/ig/StructureDefinition-PersonneStructure.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-PersonneStructure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
